--- a/src/pages/data/data_corp_projection.xlsx
+++ b/src/pages/data/data_corp_projection.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{79E279E8-B5F9-42E2-83FD-4880842C11EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72F3184D-A934-44A5-9323-44C75AA321D1}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{79E279E8-B5F9-42E2-83FD-4880842C11EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4BD28C8-388B-4499-AE03-8DAEB09860F8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{C29B67C0-CA01-4DB6-943A-35D21F1A204C}"/>
   </bookViews>
   <sheets>
     <sheet name="data_mat_proj" sheetId="1" r:id="rId1"/>
+    <sheet name="data_proj" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,12 +40,51 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
   <si>
     <t>PERIODO</t>
   </si>
   <si>
     <t>MATRICULA</t>
+  </si>
+  <si>
+    <t>UNIDAD_ACADEMICA</t>
+  </si>
+  <si>
+    <t>NIVEL</t>
+  </si>
+  <si>
+    <t>BÁSICA 1</t>
+  </si>
+  <si>
+    <t>PRE-KINDER</t>
+  </si>
+  <si>
+    <t>KINDER</t>
+  </si>
+  <si>
+    <t>1BÁSICO</t>
+  </si>
+  <si>
+    <t>2BÁSICO</t>
+  </si>
+  <si>
+    <t>3BÁSICO</t>
+  </si>
+  <si>
+    <t>4BÁSICO</t>
+  </si>
+  <si>
+    <t>5BÁSICO</t>
+  </si>
+  <si>
+    <t>6BÁSICO</t>
+  </si>
+  <si>
+    <t>7BÁSICO</t>
+  </si>
+  <si>
+    <t>8BÁSICO</t>
   </si>
 </sst>
 </file>
@@ -462,4 +502,138 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30CBF393-D5E3-45A6-B895-F44A137305EC}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/pages/data/data_corp_projection.xlsx
+++ b/src/pages/data/data_corp_projection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{79E279E8-B5F9-42E2-83FD-4880842C11EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4BD28C8-388B-4499-AE03-8DAEB09860F8}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{79E279E8-B5F9-42E2-83FD-4880842C11EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2E514AA-1159-454E-8F39-FEF9A7A2B04C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{C29B67C0-CA01-4DB6-943A-35D21F1A204C}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="23">
   <si>
     <t>PERIODO</t>
   </si>
@@ -85,16 +85,46 @@
   </si>
   <si>
     <t>8BÁSICO</t>
+  </si>
+  <si>
+    <t>BÁSICA 2</t>
+  </si>
+  <si>
+    <t>BÁSICA SF</t>
+  </si>
+  <si>
+    <t>MEDIA LOS ANDES</t>
+  </si>
+  <si>
+    <t>1MEDIO</t>
+  </si>
+  <si>
+    <t>2MEDIO</t>
+  </si>
+  <si>
+    <t>3MEDIO</t>
+  </si>
+  <si>
+    <t>4MEDIO</t>
+  </si>
+  <si>
+    <t>MEDIA SAN FELIPE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -460,43 +490,187 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC7744B-19A7-4708-BA46-6571CDE317DE}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
         <v>2024</v>
       </c>
-      <c r="B2">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="C2">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
         <v>2025</v>
       </c>
-      <c r="B3">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="C3">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
         <v>2026</v>
       </c>
-      <c r="B4">
+      <c r="C4">
         <v>635</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <v>2024</v>
+      </c>
+      <c r="C5">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6">
+        <v>2025</v>
+      </c>
+      <c r="C6">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7">
+        <v>2026</v>
+      </c>
+      <c r="C7">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8">
+        <v>2024</v>
+      </c>
+      <c r="C8">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9">
+        <v>2025</v>
+      </c>
+      <c r="C9">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10">
+        <v>2026</v>
+      </c>
+      <c r="C10">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11">
+        <v>2024</v>
+      </c>
+      <c r="C11">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12">
+        <v>2025</v>
+      </c>
+      <c r="C12">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13">
+        <v>2026</v>
+      </c>
+      <c r="C13">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14">
+        <v>2024</v>
+      </c>
+      <c r="C14">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15">
+        <v>2025</v>
+      </c>
+      <c r="C15">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16">
+        <v>2026</v>
+      </c>
+      <c r="C16">
+        <v>914</v>
       </c>
     </row>
   </sheetData>
@@ -506,7 +680,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30CBF393-D5E3-45A6-B895-F44A137305EC}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
@@ -633,7 +807,317 @@
         <v>94</v>
       </c>
     </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" t="s">
+        <v>21</v>
+      </c>
+      <c r="C35">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>22</v>
+      </c>
+      <c r="B38" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>22</v>
+      </c>
+      <c r="B39" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39">
+        <v>199</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/pages/data/data_corp_projection.xlsx
+++ b/src/pages/data/data_corp_projection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{79E279E8-B5F9-42E2-83FD-4880842C11EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2E514AA-1159-454E-8F39-FEF9A7A2B04C}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="13_ncr:1_{79E279E8-B5F9-42E2-83FD-4880842C11EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB77E994-2275-459F-A0BA-0E1E1849B0D6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{C29B67C0-CA01-4DB6-943A-35D21F1A204C}"/>
   </bookViews>
@@ -493,8 +493,9 @@
   <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/pages/data/data_corp_projection.xlsx
+++ b/src/pages/data/data_corp_projection.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="13_ncr:1_{79E279E8-B5F9-42E2-83FD-4880842C11EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB77E994-2275-459F-A0BA-0E1E1849B0D6}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="13_ncr:1_{79E279E8-B5F9-42E2-83FD-4880842C11EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE86B713-DE59-4B64-8797-3DD912D51B95}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{C29B67C0-CA01-4DB6-943A-35D21F1A204C}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="23">
   <si>
     <t>PERIODO</t>
   </si>
@@ -490,12 +490,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC7744B-19A7-4708-BA46-6571CDE317DE}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="19.85546875" customWidth="1"/>
     <col min="3" max="3" width="13.28515625" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -514,10 +515,10 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="C2">
-        <v>645</v>
+        <v>901</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -525,10 +526,10 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="C3">
-        <v>648</v>
+        <v>863</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -536,141 +537,361 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="C4">
-        <v>635</v>
+        <v>819</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B5">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C5">
-        <v>656</v>
+        <v>746</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C6">
-        <v>650</v>
+        <v>645</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B7">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C7">
-        <v>667</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B8">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C8">
-        <v>1024</v>
+        <v>635</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="C9">
-        <v>1006</v>
+        <v>750</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10">
-        <v>2026</v>
+        <v>2021</v>
       </c>
       <c r="C10">
-        <v>975</v>
+        <v>755</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B11">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C11">
-        <v>1058</v>
+        <v>705</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B12">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="C12">
-        <v>1125</v>
+        <v>653</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B13">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C13">
-        <v>1285</v>
+        <v>656</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B14">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C14">
-        <v>802</v>
+        <v>650</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B15">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C15">
-        <v>859</v>
+        <v>667</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>2020</v>
+      </c>
+      <c r="C16">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>2021</v>
+      </c>
+      <c r="C17">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>2022</v>
+      </c>
+      <c r="C18">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19">
+        <v>2023</v>
+      </c>
+      <c r="C19">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20">
+        <v>2024</v>
+      </c>
+      <c r="C20">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21">
+        <v>2025</v>
+      </c>
+      <c r="C21">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22">
+        <v>2026</v>
+      </c>
+      <c r="C22">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23">
+        <v>2020</v>
+      </c>
+      <c r="C23">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24">
+        <v>2021</v>
+      </c>
+      <c r="C24">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25">
+        <v>2022</v>
+      </c>
+      <c r="C25">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26">
+        <v>2023</v>
+      </c>
+      <c r="C26">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27">
+        <v>2024</v>
+      </c>
+      <c r="C27">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28">
+        <v>2025</v>
+      </c>
+      <c r="C28">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29">
+        <v>2026</v>
+      </c>
+      <c r="C29">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>22</v>
       </c>
-      <c r="B16">
+      <c r="B30">
+        <v>2020</v>
+      </c>
+      <c r="C30">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31">
+        <v>2021</v>
+      </c>
+      <c r="C31">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32">
+        <v>2022</v>
+      </c>
+      <c r="C32">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33">
+        <v>2023</v>
+      </c>
+      <c r="C33">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34">
+        <v>2024</v>
+      </c>
+      <c r="C34">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35">
+        <v>2025</v>
+      </c>
+      <c r="C35">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36">
         <v>2026</v>
       </c>
-      <c r="C16">
+      <c r="C36">
         <v>914</v>
       </c>
     </row>
